--- a/14_经营五表_Excel模板.xlsx
+++ b/14_经营五表_Excel模板.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORK\WANGHONGJIE-GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2264890D-A03E-4678-80CE-B611EEC47967}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7743320C-4B55-4682-B8B7-06E4BBBC0A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="764" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="768" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="使用说明" sheetId="1" r:id="rId1"/>
@@ -40,11 +40,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="240">
   <si>
     <t>《经营五表》指标口径模板 · 配套 Excel</t>
   </si>
   <si>
+    <t>《AI + 经营分析：让老板 5 分钟看懂经营真相》3 小时企业内训 · 课堂实操物料</t>
+  </si>
+  <si>
     <t>示例数据均为脱敏虚构（客户 A/B/C、华东/华南、PRJ-001…），请替换为贵司真实数据</t>
   </si>
   <si>
@@ -114,7 +117,7 @@
     <t>5. 全部做完再上 AI。口径没统一之前上 AI，只会让你更快地得到三个不一样的答案。</t>
   </si>
   <si>
-    <t>版权与联系方式：王宏杰 ｜ 19 年 LED 光电与能源电力行业 · 9 年经营分析 · 利兹大学 MBA</t>
+    <t>王宏杰 ｜ 19 年 B 端政企业务实战 · 英国利兹 MBA 商业体系 · 数据分析与大模型开发系统训练</t>
   </si>
   <si>
     <t>指标口径定义表（课堂现场填写 · 全公司统一以此为准）</t>
@@ -183,13 +186,13 @@
     <t>利润表是观点，现金流量表是事实。看现金不是看"账上有多少钱"，是看"能回来的钱"。</t>
   </si>
   <si>
-    <t>期初现金余额（元）</t>
-  </si>
-  <si>
-    <t>当前现金余额</t>
-  </si>
-  <si>
-    <t>近 3 月平均净流出</t>
+    <t>期初现金余额（元 · 2026-01）</t>
+  </si>
+  <si>
+    <t>期末现金余额（2026-12）</t>
+  </si>
+  <si>
+    <t>近 3 月平均净流出（10-12 月）</t>
   </si>
   <si>
     <t>可支撑月数</t>
@@ -300,7 +303,7 @@
     <t>合计</t>
   </si>
   <si>
-    <t>💡 课堂话术：很多老板看到"账上有 300 万"就安心了。但把账龄一拉，180 天以上的 29 万大概率收不回来、90-180 天的 42 万要打对折——真实能用的钱要往下修 50 万以上。</t>
+    <t>📌 读表要点：可支撑月数 = 期末现金 ÷ 月均净流出 = 210 万 ÷ 32.3 万 ≈ 6.5 个月。安全线通常按 6 个月设，本表刚好压线——要么加速回款，要么把部分支出后移。更关键的是应收这一端：账面应收 214.8 万，按各账龄区间预计回收率加权后，真实可回收约 156 万，差额 58.5 万（占账面 27%）。做资金计划按 156 万排，不要按 214.8 万排。口径校验：本表应收合计与表⑤互为验证——年营收 1207 万 × 加权 DSO 65 天 ÷ 365 ≈ 215 万，与本表合计一致。</t>
   </si>
   <si>
     <t>表② 收入结构表 —— 钱从哪来</t>
@@ -309,7 +312,7 @@
     <t>最危险的结构，是一个客户占你 40% 以上。盯住"前 20% 客户贡献占比"。</t>
   </si>
   <si>
-    <t>总营收（YTD）</t>
+    <t>Top12 客户收入（元）</t>
   </si>
   <si>
     <t>前 20% 客户贡献</t>
@@ -321,439 +324,442 @@
     <t>集中度判定</t>
   </si>
   <si>
+    <t>Top12 客户（脱敏）</t>
+  </si>
+  <si>
+    <t>年度收入（元）</t>
+  </si>
+  <si>
+    <t>收入占比</t>
+  </si>
+  <si>
+    <t>累计占比</t>
+  </si>
+  <si>
+    <t>产品线</t>
+  </si>
+  <si>
+    <t>收入（元）</t>
+  </si>
+  <si>
+    <t>客户 A</t>
+  </si>
+  <si>
+    <t>显示系统 P1</t>
+  </si>
+  <si>
+    <t>客户 B</t>
+  </si>
+  <si>
+    <t>照明工程 P2</t>
+  </si>
+  <si>
+    <t>客户 C</t>
+  </si>
+  <si>
+    <t>能源服务 P3</t>
+  </si>
+  <si>
+    <t>客户 D</t>
+  </si>
+  <si>
+    <t>客户 E</t>
+  </si>
+  <si>
+    <t>客户 F</t>
+  </si>
+  <si>
+    <t>客户 G</t>
+  </si>
+  <si>
+    <t>客户 H</t>
+  </si>
+  <si>
+    <t>客户 I</t>
+  </si>
+  <si>
+    <t>客户 J</t>
+  </si>
+  <si>
+    <t>客户 K</t>
+  </si>
+  <si>
+    <t>客户 L</t>
+  </si>
+  <si>
+    <t>区域维度（脱敏示例）</t>
+  </si>
+  <si>
+    <t>区域</t>
+  </si>
+  <si>
+    <t>同比</t>
+  </si>
+  <si>
+    <t>华东</t>
+  </si>
+  <si>
+    <t>华南</t>
+  </si>
+  <si>
+    <t>华北</t>
+  </si>
+  <si>
+    <t>西南</t>
+  </si>
+  <si>
+    <t>西北</t>
+  </si>
+  <si>
+    <t>📌 读表要点：前 20% 客户（3 家）贡献 57% 收入，第一大客户占 24.5%，已接近 25% 的集中度警戒线。收入越集中，单客户流失对全年业绩的冲击越大——建议对占比超 15% 的客户单独建立维护台账与流失预警。维度校验：产品线与区域两个维度合计均为 1207 万（＝年度总营收）；客户维度列示的是前 12 大客户，合计 1169.5 万、占年营收 96.9%，其余为长尾零散客户。换成真实数据后如果两个维度对不上，说明口径还没统一，先回去填《指标口径定义表》。</t>
+  </si>
+  <si>
+    <t>表③ 项目 / 产品盈亏表 —— 哪个生意真的赚钱</t>
+  </si>
+  <si>
+    <t>营收涨了利润没涨，问题一定出在这一张表。低于毛利率底线的单子，做得越大亏得越多。</t>
+  </si>
+  <si>
+    <t>毛利率底线</t>
+  </si>
+  <si>
+    <t>低于底线的项目数</t>
+  </si>
+  <si>
+    <t>加权毛利率</t>
+  </si>
+  <si>
+    <t>项目编号</t>
+  </si>
+  <si>
+    <t>合同额（元）</t>
+  </si>
+  <si>
+    <t>直接成本</t>
+  </si>
+  <si>
+    <t>分摊费用（按合同额 10%）</t>
+  </si>
+  <si>
+    <t>毛利（元）</t>
+  </si>
+  <si>
+    <t>判定</t>
+  </si>
+  <si>
+    <t>处理建议</t>
+  </si>
+  <si>
+    <t>PRJ-001</t>
+  </si>
+  <si>
+    <t>PRJ-002</t>
+  </si>
+  <si>
+    <t>PRJ-003</t>
+  </si>
+  <si>
+    <t>PRJ-004</t>
+  </si>
+  <si>
+    <t>PRJ-005</t>
+  </si>
+  <si>
+    <t>PRJ-006</t>
+  </si>
+  <si>
+    <t>PRJ-007</t>
+  </si>
+  <si>
+    <t>PRJ-008</t>
+  </si>
+  <si>
+    <t>PRJ-009</t>
+  </si>
+  <si>
+    <t>PRJ-010</t>
+  </si>
+  <si>
+    <t>📌 读表要点：PRJ-010 合同额 28 万，毛利率仅 7.1%，远低于 25% 的底线——这类订单不是生意，是占用交付资源还倒贴管理成本。判断一笔订单的优先级，先问“拿下了值不值”，再问“能不能拿下”。注意本表 10 个在执行的重点项目合计合同额 893 万、约占年营收 74%，其中 7 个低于底线、加权毛利率 22.2%——问题不在单个项目，而在报价体系或成本结构，逐单救火解决不了。</t>
+  </si>
+  <si>
+    <t>表④ 漏斗与预测表 —— 下季度能收多少</t>
+  </si>
+  <si>
+    <t>没有预测的复盘都是马后炮。给每个商机打中标概率分，用概率加权，不要拍脑袋。</t>
+  </si>
+  <si>
+    <t>商机总金额</t>
+  </si>
+  <si>
+    <t>概率加权预测</t>
+  </si>
+  <si>
+    <t>加权/总额</t>
+  </si>
+  <si>
+    <t>本季度预计签约（Q4）</t>
+  </si>
+  <si>
+    <t>商机编号</t>
+  </si>
+  <si>
     <t>客户（脱敏）</t>
   </si>
   <si>
-    <t>年度收入（元）</t>
-  </si>
-  <si>
-    <t>收入占比</t>
-  </si>
-  <si>
-    <t>累计占比</t>
-  </si>
-  <si>
-    <t>产品线</t>
-  </si>
-  <si>
-    <t>收入（元）</t>
-  </si>
-  <si>
-    <t>客户 A</t>
-  </si>
-  <si>
-    <t>显示系统 P1</t>
-  </si>
-  <si>
-    <t>客户 B</t>
-  </si>
-  <si>
-    <t>照明工程 P2</t>
-  </si>
-  <si>
-    <t>客户 C</t>
-  </si>
-  <si>
-    <t>能源服务 P3</t>
-  </si>
-  <si>
-    <t>客户 D</t>
-  </si>
-  <si>
-    <t>客户 E</t>
-  </si>
-  <si>
-    <t>客户 F</t>
-  </si>
-  <si>
-    <t>客户 G</t>
-  </si>
-  <si>
-    <t>客户 H</t>
-  </si>
-  <si>
-    <t>客户 I</t>
-  </si>
-  <si>
-    <t>客户 J</t>
-  </si>
-  <si>
-    <t>客户 K</t>
-  </si>
-  <si>
-    <t>客户 L</t>
-  </si>
-  <si>
-    <t>区域维度（脱敏示例）</t>
-  </si>
-  <si>
-    <t>区域</t>
-  </si>
-  <si>
-    <t>同比</t>
-  </si>
-  <si>
-    <t>华东</t>
-  </si>
-  <si>
-    <t>华南</t>
-  </si>
-  <si>
-    <t>华北</t>
-  </si>
-  <si>
-    <t>西南</t>
-  </si>
-  <si>
-    <t>西北</t>
-  </si>
-  <si>
-    <t>💡 课堂话术：前 20% 客户（约 2-3 家）贡献 55% 收入。这意味着其中任何一家流失，你当年营收立刻掉一半。这一页通常能让老板当场拿出手机打电话。</t>
-  </si>
-  <si>
-    <t>表③ 项目 / 产品盈亏表 —— 哪个生意真的赚钱</t>
-  </si>
-  <si>
-    <t>营收涨了利润没涨，问题一定出在这一张表。低于毛利率底线的单子，做得越大亏得越多。</t>
-  </si>
-  <si>
-    <t>毛利率底线</t>
-  </si>
-  <si>
-    <t>低于底线的项目数</t>
-  </si>
-  <si>
-    <t>加权毛利率</t>
-  </si>
-  <si>
-    <t>项目编号</t>
-  </si>
-  <si>
-    <t>合同额（元）</t>
-  </si>
-  <si>
-    <t>直接成本</t>
-  </si>
-  <si>
-    <t>分摊费用</t>
-  </si>
-  <si>
-    <t>毛利（元）</t>
+    <t>当前阶段</t>
+  </si>
+  <si>
+    <t>中标概率</t>
+  </si>
+  <si>
+    <t>加权金额</t>
+  </si>
+  <si>
+    <t>停留天数</t>
+  </si>
+  <si>
+    <t>预计签约</t>
+  </si>
+  <si>
+    <t>OPP-001</t>
+  </si>
+  <si>
+    <t>商务谈判</t>
+  </si>
+  <si>
+    <t>2026-Q4</t>
+  </si>
+  <si>
+    <t>OPP-002</t>
+  </si>
+  <si>
+    <t>报价</t>
+  </si>
+  <si>
+    <t>OPP-003</t>
+  </si>
+  <si>
+    <t>OPP-004</t>
+  </si>
+  <si>
+    <t>方案确认</t>
+  </si>
+  <si>
+    <t>OPP-005</t>
+  </si>
+  <si>
+    <t>OPP-006</t>
+  </si>
+  <si>
+    <t>初步接触</t>
+  </si>
+  <si>
+    <t>2027-Q1</t>
+  </si>
+  <si>
+    <t>OPP-007</t>
+  </si>
+  <si>
+    <t>OPP-008</t>
+  </si>
+  <si>
+    <t>OPP-009</t>
+  </si>
+  <si>
+    <t>中标待签</t>
+  </si>
+  <si>
+    <t>OPP-010</t>
+  </si>
+  <si>
+    <t>OPP-011</t>
+  </si>
+  <si>
+    <t>OPP-012</t>
+  </si>
+  <si>
+    <t>OPP-013</t>
+  </si>
+  <si>
+    <t>客户 M</t>
+  </si>
+  <si>
+    <t>OPP-014</t>
+  </si>
+  <si>
+    <t>客户 N</t>
+  </si>
+  <si>
+    <t>OPP-015</t>
+  </si>
+  <si>
+    <t>客户 O</t>
+  </si>
+  <si>
+    <t>📌 使用提示：停留超过 40 天的商机已自动标红（OPP-001 停留 42 天、OPP-003 停留 55 天、OPP-008 停留 47 天）。把这条规则固化进周会，能在月中就识别出停滞商机，而不是等到月底复盘才知道输了。另注意 OPP-003 已停留 55 天却仍挂在 80% 概率——概率没有随停留天数下调，会系统性高估预测（本表概率加权预测 488 万，占商机总额 54%）。建议把“停留超 40 天自动降一档概率”写进规则。</t>
+  </si>
+  <si>
+    <t>表⑤ 人效与回款表 —— 钱收得回来吗、人用得值吗</t>
+  </si>
+  <si>
+    <t>回款周期每缩短 15 天，等于白赚一笔无息贷款。人越招越多、人均产出却在降，是最容易被忽略的失血点。</t>
+  </si>
+  <si>
+    <t>团队总人数</t>
+  </si>
+  <si>
+    <t>人均营收（元）</t>
+  </si>
+  <si>
+    <t>整体回款率</t>
+  </si>
+  <si>
+    <t>加权平均 DSO（天）</t>
+  </si>
+  <si>
+    <t>区域/团队</t>
+  </si>
+  <si>
+    <t>人数</t>
+  </si>
+  <si>
+    <t>营收（元）</t>
+  </si>
+  <si>
+    <t>回款额（元）</t>
+  </si>
+  <si>
+    <t>回款率</t>
+  </si>
+  <si>
+    <t>DSO（天）</t>
+  </si>
+  <si>
+    <t>逾期金额</t>
+  </si>
+  <si>
+    <t>逾期占营收</t>
+  </si>
+  <si>
+    <t>华东区</t>
+  </si>
+  <si>
+    <t>华南区</t>
+  </si>
+  <si>
+    <t>华北区</t>
+  </si>
+  <si>
+    <t>西南区</t>
+  </si>
+  <si>
+    <t>西北区</t>
+  </si>
+  <si>
+    <t>📌 读表要点：西北区 DSO 95 天最长、回款率 80.2% 最低，但逾期占营收 17.4% 并非最高——它的特征是“回款慢”而不是“收不回”，通常指向账期政策或大客户占比；西南区 DSO 83 天、逾期占营收 18.9% 最高，特征才是“回款质量差”，指向客户信用风险。两者整改动作不同：前者调账期与结算条款，后者改客户准入与催收节奏。另注意西北区人均营收 28.7 万，仅为华东（53.3 万）的 54%，人效差距需单独归因，不能默认等同于回款问题。若把西北 DSO 从 95 天压到 60 天，按本区营收测算约释放 8.2 万资金占用。口径提醒：整体 DSO 按营收加权为 65 天，若用简单平均会得到 71 天——小区域与大盘被同等对待会放大偏差，这个口径要写死在《指标口径定义表》里。本表逾期合计 129.3 万（账期 60 天口径），与表①账龄中 61 天以上的 129.3 万完全对应，两张表可交叉核对。</t>
+  </si>
+  <si>
+    <t>《30 天落地行动卡》</t>
+  </si>
+  <si>
+    <t>今天回去不用做五张表，先做第一张现金表。做出来你就会发现，第二张第三张自己就长出来了。</t>
+  </si>
+  <si>
+    <t>周次</t>
+  </si>
+  <si>
+    <t>本周要做的三件事</t>
+  </si>
+  <si>
+    <t>交付物（能拿出来看的）</t>
+  </si>
+  <si>
+    <t>自检（打勾）</t>
+  </si>
+  <si>
+    <t>负责人</t>
+  </si>
+  <si>
+    <t>第 1 周</t>
+  </si>
+  <si>
+    <t>把 5 个核心指标的口径写死（销售额/回款/毛利/商机/活跃客户）</t>
+  </si>
+  <si>
+    <t>《指标口径定义表》1 页，已签字已群发</t>
+  </si>
+  <si>
+    <t>☐ 已完成</t>
+  </si>
+  <si>
+    <t>全公司发一次，让财务、销售、运营三方签字确认</t>
+  </si>
+  <si>
+    <t>指定"唯一数字权威"——谁的数说了算</t>
+  </si>
+  <si>
+    <t>第 2 周</t>
+  </si>
+  <si>
+    <t>拉出现金余额 + 近 3 月平均净流出 → 算出可支撑月数</t>
+  </si>
+  <si>
+    <t>表①现金表 + 表②收入结构表（各 1 页）</t>
+  </si>
+  <si>
+    <t>把应收账款按账龄分段，算出真实可收回金额</t>
+  </si>
+  <si>
+    <t>把客户按收入从大到小排，算出前 20% 贡献占比</t>
+  </si>
+  <si>
+    <t>第 3 周</t>
+  </si>
+  <si>
+    <t>给每个在途商机打中标概率分（初步接触 15% / 方案 35% / 报价 50% / 谈判 80% / 待签 95%）</t>
+  </si>
+  <si>
+    <t>表④漏斗预测表 + 高风险商机清单</t>
+  </si>
+  <si>
+    <t>算出概率加权预测，得出下季度预计签约额</t>
+  </si>
+  <si>
+    <t>拉出停留超 40 天的商机，逐个过一遍</t>
+  </si>
+  <si>
+    <t>第 4 周</t>
+  </si>
+  <si>
+    <t>选一个 AI 场景落地试跑（推荐：口语问数 或 制度知识库）</t>
+  </si>
+  <si>
+    <t>一个能跑通的 AI 场景 Demo（截图即可）</t>
+  </si>
+  <si>
+    <t>接一张自己的 Excel 表，试问三个问题</t>
+  </si>
+  <si>
+    <t>把结果发到公司群里，让老板看到</t>
+  </si>
+  <si>
+    <t>🔴 三条纪律</t>
+  </si>
+  <si>
+    <t>1. 口径没统一之前，不要上 AI —— 否则你只会更快地得到三个不一样的答案。</t>
+  </si>
+  <si>
+    <t>2. 每周只做一张表，做完再往下走。五张表同时开工，通常一张都做不完。</t>
+  </si>
+  <si>
+    <t>3. 任何 AI 出的数，都要能追溯到原始表。追不回去的数，不要拿去做决策。</t>
+  </si>
+  <si>
+    <t>卡住了随时找：王宏杰 ｜ 19 年 B 端政企业务实战 · 英国利兹 MBA 商业体系 · 数据分析与大模型开发系统训练 ｜ 微信/手机：189 1098 9990 ｜ 272702947@qq.com</t>
   </si>
   <si>
     <t>判定</t>
-  </si>
-  <si>
-    <t>处理建议</t>
-  </si>
-  <si>
-    <t>PRJ-001</t>
-  </si>
-  <si>
-    <t>PRJ-002</t>
-  </si>
-  <si>
-    <t>PRJ-003</t>
-  </si>
-  <si>
-    <t>PRJ-004</t>
-  </si>
-  <si>
-    <t>PRJ-005</t>
-  </si>
-  <si>
-    <t>PRJ-006</t>
-  </si>
-  <si>
-    <t>PRJ-007</t>
-  </si>
-  <si>
-    <t>PRJ-008</t>
-  </si>
-  <si>
-    <t>PRJ-009</t>
-  </si>
-  <si>
-    <t>PRJ-010</t>
-  </si>
-  <si>
-    <t>💡 课堂话术：PRJ-010 合同额 28 万，毛利率只有 7.1%——这种单子不是生意，是给客户打工还贴了管理成本。真正该问的不是"能不能拿下"，是"拿下了值不值"。</t>
-  </si>
-  <si>
-    <t>表④ 漏斗与预测表 —— 下季度能收多少</t>
-  </si>
-  <si>
-    <t>没有预测的复盘都是马后炮。给每个商机打中标概率分，用概率加权，不要拍脑袋。</t>
-  </si>
-  <si>
-    <t>商机总金额</t>
-  </si>
-  <si>
-    <t>概率加权预测</t>
-  </si>
-  <si>
-    <t>加权/总额</t>
-  </si>
-  <si>
-    <t>本季度预计签约（Q4）</t>
-  </si>
-  <si>
-    <t>商机编号</t>
-  </si>
-  <si>
-    <t>当前阶段</t>
-  </si>
-  <si>
-    <t>中标概率</t>
-  </si>
-  <si>
-    <t>加权金额</t>
-  </si>
-  <si>
-    <t>停留天数</t>
-  </si>
-  <si>
-    <t>预计签约</t>
-  </si>
-  <si>
-    <t>OPP-001</t>
-  </si>
-  <si>
-    <t>商务谈判</t>
-  </si>
-  <si>
-    <t>2026-Q4</t>
-  </si>
-  <si>
-    <t>OPP-002</t>
-  </si>
-  <si>
-    <t>报价</t>
-  </si>
-  <si>
-    <t>OPP-003</t>
-  </si>
-  <si>
-    <t>OPP-004</t>
-  </si>
-  <si>
-    <t>方案确认</t>
-  </si>
-  <si>
-    <t>OPP-005</t>
-  </si>
-  <si>
-    <t>OPP-006</t>
-  </si>
-  <si>
-    <t>初步接触</t>
-  </si>
-  <si>
-    <t>2027-Q1</t>
-  </si>
-  <si>
-    <t>OPP-007</t>
-  </si>
-  <si>
-    <t>OPP-008</t>
-  </si>
-  <si>
-    <t>OPP-009</t>
-  </si>
-  <si>
-    <t>中标待签</t>
-  </si>
-  <si>
-    <t>OPP-010</t>
-  </si>
-  <si>
-    <t>OPP-011</t>
-  </si>
-  <si>
-    <t>OPP-012</t>
-  </si>
-  <si>
-    <t>OPP-013</t>
-  </si>
-  <si>
-    <t>客户 M</t>
-  </si>
-  <si>
-    <t>OPP-014</t>
-  </si>
-  <si>
-    <t>客户 N</t>
-  </si>
-  <si>
-    <t>OPP-015</t>
-  </si>
-  <si>
-    <t>客户 O</t>
-  </si>
-  <si>
-    <t>💡 高风险清单：停留超过 40 天的商机自动标红（OPP-003 已停 55 天、OPP-008 已停 47 天）。以前是月底复盘才知道输了，现在周中就预警，还来得及救。</t>
-  </si>
-  <si>
-    <t>表⑤ 人效与回款表 —— 钱收得回来吗、人用得值吗</t>
-  </si>
-  <si>
-    <t>回款周期每缩短 15 天，等于白赚一笔无息贷款。人越招越多、人均产出却在降，是最容易被忽略的失血点。</t>
-  </si>
-  <si>
-    <t>团队总人数</t>
-  </si>
-  <si>
-    <t>人均营收（元）</t>
-  </si>
-  <si>
-    <t>整体回款率</t>
-  </si>
-  <si>
-    <t>平均 DSO（天）</t>
-  </si>
-  <si>
-    <t>区域/团队</t>
-  </si>
-  <si>
-    <t>人数</t>
-  </si>
-  <si>
-    <t>营收（元）</t>
-  </si>
-  <si>
-    <t>回款额（元）</t>
-  </si>
-  <si>
-    <t>回款率</t>
-  </si>
-  <si>
-    <t>DSO（天）</t>
-  </si>
-  <si>
-    <t>逾期金额</t>
-  </si>
-  <si>
-    <t>逾期占比</t>
-  </si>
-  <si>
-    <t>华东区</t>
-  </si>
-  <si>
-    <t>华南区</t>
-  </si>
-  <si>
-    <t>华北区</t>
-  </si>
-  <si>
-    <t>西南区</t>
-  </si>
-  <si>
-    <t>西北区</t>
-  </si>
-  <si>
-    <t>💡 课堂话术：西北区 3 个人，DSO 95 天，逾期 22.4 万占营收 26%——这个区域不是不努力，是客户结构有问题。华南区 DSO 72 天也要盯。把 DSO 从 95 天压到 60 天，等于凭空多出 35 天营运资金。</t>
-  </si>
-  <si>
-    <t>《30 天落地行动卡》</t>
-  </si>
-  <si>
-    <t>今天回去不用做五张表，先做第一张现金表。做出来你就会发现，第二张第三张自己就长出来了。</t>
-  </si>
-  <si>
-    <t>周次</t>
-  </si>
-  <si>
-    <t>本周要做的三件事</t>
-  </si>
-  <si>
-    <t>交付物（能拿出来看的）</t>
-  </si>
-  <si>
-    <t>自检（打勾）</t>
-  </si>
-  <si>
-    <t>负责人</t>
-  </si>
-  <si>
-    <t>第 1 周</t>
-  </si>
-  <si>
-    <t>把 5 个核心指标的口径写死（销售额/回款/毛利/商机/活跃客户）</t>
-  </si>
-  <si>
-    <t>《指标口径定义表》1 页，已签字已群发</t>
-  </si>
-  <si>
-    <t>☐ 已完成</t>
-  </si>
-  <si>
-    <t>全公司发一次，让财务、销售、运营三方签字确认</t>
-  </si>
-  <si>
-    <t>指定"唯一数字权威"——谁的数说了算</t>
-  </si>
-  <si>
-    <t>第 2 周</t>
-  </si>
-  <si>
-    <t>拉出现金余额 + 近 3 月平均净流出 → 算出可支撑月数</t>
-  </si>
-  <si>
-    <t>表①现金表 + 表②收入结构表（各 1 页）</t>
-  </si>
-  <si>
-    <t>把应收账款按账龄分段，算出真实可收回金额</t>
-  </si>
-  <si>
-    <t>把客户按收入从大到小排，算出前 20% 贡献占比</t>
-  </si>
-  <si>
-    <t>第 3 周</t>
-  </si>
-  <si>
-    <t>给每个在途商机打中标概率分（初步接触 15% / 方案 35% / 报价 50% / 谈判 80% / 待签 95%）</t>
-  </si>
-  <si>
-    <t>表④漏斗预测表 + 高风险商机清单</t>
-  </si>
-  <si>
-    <t>算出概率加权预测，得出下季度预计签约额</t>
-  </si>
-  <si>
-    <t>拉出停留超 40 天的商机，逐个过一遍</t>
-  </si>
-  <si>
-    <t>第 4 周</t>
-  </si>
-  <si>
-    <t>选一个 AI 场景落地试跑（推荐：口语问数 或 制度知识库）</t>
-  </si>
-  <si>
-    <t>一个能跑通的 AI 场景 Demo（截图即可）</t>
-  </si>
-  <si>
-    <t>接一张自己的 Excel 表，试问三个问题</t>
-  </si>
-  <si>
-    <t>把结果发到公司群里，让老板看到</t>
-  </si>
-  <si>
-    <t>🔴 三条纪律</t>
-  </si>
-  <si>
-    <t>1. 口径没统一之前，不要上 AI —— 否则你只会更快地得到三个不一样的答案。</t>
-  </si>
-  <si>
-    <t>2. 每周只做一张表，做完再往下走。五张表同时开工，通常一张都做不完。</t>
-  </si>
-  <si>
-    <t>3. 任何 AI 出的数，都要能追溯到原始表。追不回去的数，不要拿去做决策。</t>
-  </si>
-  <si>
-    <t>卡住了随时找：王宏杰 ｜ 19 年 LED 光电与能源电力行业 · 9 年经营分析 · 利兹大学 MBA ｜ 微信/手机：189 1098 9990 ｜ 272702947@qq.com</t>
-  </si>
-  <si>
-    <t>《AI + 经营分析：让老板 5 分钟看懂经营真相》3 小时企业内训 · 课堂实操物料</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
@@ -901,7 +907,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -995,21 +1001,24 @@
     <xf numFmtId="1" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1017,47 +1026,11 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="10">
     <dxf>
       <font>
         <b/>
@@ -1135,6 +1108,14 @@
     </dxf>
     <dxf>
       <font>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFC0392B"/>
+        <name val="微软雅黑"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <sz val="10"/>
         <color rgb="FFC0392B"/>
         <name val="微软雅黑"/>
@@ -1152,6 +1133,11 @@
         <color rgb="FFC0392B"/>
         <name val="微软雅黑"/>
       </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFDECEA"/>
+        </patternFill>
+      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1459,142 +1445,142 @@
     <col min="3" max="3" width="86" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" ht="45.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="39" t="s">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B2" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="39"/>
-    </row>
-    <row r="3" spans="2:3" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="40" t="s">
-        <v>237</v>
-      </c>
-      <c r="C3" s="40"/>
-    </row>
-    <row r="4" spans="2:3" ht="23.65" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="40" t="s">
+      <c r="C2" s="37"/>
+    </row>
+    <row r="3" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B3" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="40"/>
+      <c r="C3" s="37"/>
+    </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B4" s="39" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="37"/>
     </row>
     <row r="6" spans="2:3" ht="14.65" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" spans="2:3" ht="26.65" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="41"/>
+    </row>
+    <row r="15" spans="2:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="42"/>
     </row>
     <row r="16" spans="2:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="C16" s="36"/>
+      <c r="B16" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="37"/>
     </row>
     <row r="17" spans="2:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="35" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17" s="36"/>
+      <c r="B17" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17" s="37"/>
     </row>
     <row r="18" spans="2:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="35" t="s">
-        <v>21</v>
-      </c>
-      <c r="C18" s="36"/>
+      <c r="B18" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" s="37"/>
     </row>
     <row r="19" spans="2:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="35" t="s">
-        <v>22</v>
-      </c>
-      <c r="C19" s="36"/>
+      <c r="B19" s="36" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" s="37"/>
     </row>
     <row r="20" spans="2:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="35" t="s">
-        <v>23</v>
-      </c>
-      <c r="C20" s="36"/>
+      <c r="B20" s="36" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" s="37"/>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B22" s="37" t="s">
-        <v>24</v>
-      </c>
-      <c r="C22" s="36"/>
+      <c r="B22" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="C22" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1615,58 +1601,58 @@
     <col min="8" max="8" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="40.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="39" t="s">
-        <v>25</v>
-      </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-    </row>
-    <row r="2" spans="1:8" ht="24.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="40" t="s">
+    <row r="1" spans="1:8" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="40"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="39" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
     </row>
     <row r="4" spans="1:8" ht="26" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5"/>
       <c r="B4" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="6"/>
       <c r="B5" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C5" s="6"/>
       <c r="D5" s="6"/>
@@ -1678,7 +1664,7 @@
     <row r="6" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7"/>
       <c r="B6" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
@@ -1690,7 +1676,7 @@
     <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6"/>
       <c r="B7" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
@@ -1702,7 +1688,7 @@
     <row r="8" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7"/>
       <c r="B8" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
@@ -1714,7 +1700,7 @@
     <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
       <c r="B9" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C9" s="6"/>
       <c r="D9" s="6"/>
@@ -1726,7 +1712,7 @@
     <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7"/>
       <c r="B10" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -1738,7 +1724,7 @@
     <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="6"/>
       <c r="B11" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C11" s="6"/>
       <c r="D11" s="6"/>
@@ -1750,7 +1736,7 @@
     <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7"/>
       <c r="B12" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
@@ -1762,7 +1748,7 @@
     <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6"/>
       <c r="B13" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
@@ -1774,7 +1760,7 @@
     <row r="14" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="7"/>
       <c r="B14" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
@@ -1783,23 +1769,23 @@
       <c r="G14" s="7"/>
       <c r="H14" s="7"/>
     </row>
-    <row r="16" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="38" t="s">
-        <v>44</v>
-      </c>
-      <c r="B16" s="36"/>
-      <c r="C16" s="36"/>
-      <c r="D16" s="36"/>
-      <c r="E16" s="36"/>
-      <c r="F16" s="36"/>
-      <c r="G16" s="36"/>
-      <c r="H16" s="36"/>
+    <row r="16" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="37"/>
+      <c r="C16" s="37"/>
+      <c r="D16" s="37"/>
+      <c r="E16" s="37"/>
+      <c r="F16" s="37"/>
+      <c r="G16" s="37"/>
+      <c r="H16" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A2:H2"/>
     <mergeCell ref="A16:H16"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <dataValidations count="1">
@@ -1819,94 +1805,94 @@
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="18.06640625" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
     <col min="7" max="7" width="15" customWidth="1"/>
     <col min="8" max="8" width="20" customWidth="1"/>
     <col min="9" max="9" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="39" t="s">
-        <v>45</v>
-      </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-    </row>
-    <row r="2" spans="1:9" ht="29.35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="40" t="s">
+    <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="38" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="40"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="40"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" s="39" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
+      <c r="I2" s="37"/>
     </row>
     <row r="4" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C4" s="8">
         <v>1850000</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E4" s="8">
         <f>C4+SUM(E8:E19)</f>
-        <v>3390000</v>
+        <v>2100000</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G4" s="8">
         <f>-AVERAGE(E17:E19)</f>
-        <v>-106666.66666666667</v>
+        <v>323333.33333333331</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I4" s="9" t="str">
         <f>IF(G4&lt;=0,"净流入，安全",ROUND(E4/G4,1)&amp;" 个月")</f>
-        <v>净流入，安全</v>
+        <v>6.5 个月</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="26" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5"/>
       <c r="B7" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G7" s="5"/>
       <c r="H7" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I7" s="5"/>
     </row>
     <row r="8" spans="1:9" ht="13.9" x14ac:dyDescent="0.3">
       <c r="A8" s="6"/>
       <c r="B8" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C8" s="10">
         <v>1420000</v>
@@ -1926,7 +1912,7 @@
     <row r="9" spans="1:9" ht="13.9" x14ac:dyDescent="0.3">
       <c r="A9" s="7"/>
       <c r="B9" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C9" s="12">
         <v>1180000</v>
@@ -1946,7 +1932,7 @@
     <row r="10" spans="1:9" ht="13.9" x14ac:dyDescent="0.3">
       <c r="A10" s="6"/>
       <c r="B10" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C10" s="10">
         <v>1650000</v>
@@ -1966,7 +1952,7 @@
     <row r="11" spans="1:9" ht="13.9" x14ac:dyDescent="0.3">
       <c r="A11" s="7"/>
       <c r="B11" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C11" s="12">
         <v>1310000</v>
@@ -1986,7 +1972,7 @@
     <row r="12" spans="1:9" ht="13.9" x14ac:dyDescent="0.3">
       <c r="A12" s="6"/>
       <c r="B12" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C12" s="10">
         <v>1480000</v>
@@ -2006,7 +1992,7 @@
     <row r="13" spans="1:9" ht="13.9" x14ac:dyDescent="0.3">
       <c r="A13" s="7"/>
       <c r="B13" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C13" s="12">
         <v>1720000</v>
@@ -2026,7 +2012,7 @@
     <row r="14" spans="1:9" ht="13.9" x14ac:dyDescent="0.3">
       <c r="A14" s="6"/>
       <c r="B14" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C14" s="10">
         <v>1390000</v>
@@ -2046,7 +2032,7 @@
     <row r="15" spans="1:9" ht="13.9" x14ac:dyDescent="0.3">
       <c r="A15" s="7"/>
       <c r="B15" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C15" s="12">
         <v>1560000</v>
@@ -2066,7 +2052,7 @@
     <row r="16" spans="1:9" ht="13.9" x14ac:dyDescent="0.3">
       <c r="A16" s="6"/>
       <c r="B16" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C16" s="10">
         <v>1810000</v>
@@ -2086,202 +2072,202 @@
     <row r="17" spans="1:9" ht="13.9" x14ac:dyDescent="0.3">
       <c r="A17" s="7"/>
       <c r="B17" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C17" s="12">
         <v>1250000</v>
       </c>
       <c r="D17" s="12">
-        <v>1370000</v>
+        <v>1620000</v>
       </c>
       <c r="E17" s="13">
         <f t="shared" si="0"/>
-        <v>-120000</v>
+        <v>-370000</v>
       </c>
       <c r="F17" s="13">
         <f t="shared" si="1"/>
-        <v>2950000</v>
+        <v>2700000</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="13.9" x14ac:dyDescent="0.3">
       <c r="A18" s="6"/>
       <c r="B18" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C18" s="10">
         <v>1490000</v>
       </c>
       <c r="D18" s="10">
-        <v>1420000</v>
+        <v>1780000</v>
       </c>
       <c r="E18" s="11">
         <f t="shared" si="0"/>
-        <v>70000</v>
+        <v>-290000</v>
       </c>
       <c r="F18" s="11">
         <f t="shared" si="1"/>
-        <v>3020000</v>
+        <v>2410000</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="13.9" x14ac:dyDescent="0.3">
       <c r="A19" s="7"/>
       <c r="B19" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C19" s="12">
         <v>1950000</v>
       </c>
       <c r="D19" s="12">
-        <v>1580000</v>
+        <v>2260000</v>
       </c>
       <c r="E19" s="13">
         <f t="shared" si="0"/>
-        <v>370000</v>
+        <v>-310000</v>
       </c>
       <c r="F19" s="13">
         <f t="shared" si="1"/>
-        <v>3390000</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="42" t="s">
-        <v>69</v>
-      </c>
-      <c r="B21" s="42"/>
-      <c r="C21" s="42"/>
-      <c r="D21" s="42"/>
-      <c r="E21" s="42"/>
-      <c r="F21" s="42"/>
-      <c r="G21" s="42"/>
-      <c r="H21" s="42"/>
-      <c r="I21" s="42"/>
+        <v>2100000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="43" t="s">
+        <v>70</v>
+      </c>
+      <c r="B21" s="43"/>
+      <c r="C21" s="43"/>
+      <c r="D21" s="43"/>
+      <c r="E21" s="43"/>
+      <c r="F21" s="43"/>
+      <c r="G21" s="43"/>
+      <c r="H21" s="43"/>
+      <c r="I21" s="43"/>
     </row>
     <row r="22" spans="1:9" ht="26" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5"/>
       <c r="B22" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G22" s="5"/>
       <c r="H22" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I22" s="5"/>
     </row>
     <row r="23" spans="1:9" ht="14.65" x14ac:dyDescent="0.45">
       <c r="A23" s="6"/>
       <c r="B23" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C23" s="10">
-        <v>2680000</v>
+        <v>520000</v>
       </c>
       <c r="D23" s="14">
         <f>C23/SUM($C$23:$C$27)</f>
-        <v>0.50470809792843696</v>
+        <v>0.24208566108007448</v>
       </c>
       <c r="E23" s="15">
         <v>0.98</v>
       </c>
       <c r="F23" s="11">
         <f>C23*E23</f>
-        <v>2626400</v>
+        <v>509600</v>
       </c>
       <c r="H23" s="16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="14.65" x14ac:dyDescent="0.45">
       <c r="A24" s="7"/>
       <c r="B24" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C24" s="12">
-        <v>1240000</v>
+        <v>335000</v>
       </c>
       <c r="D24" s="17">
         <f>C24/SUM($C$23:$C$27)</f>
-        <v>0.2335216572504708</v>
+        <v>0.15595903165735567</v>
       </c>
       <c r="E24" s="18">
         <v>0.92</v>
       </c>
       <c r="F24" s="13">
         <f>C24*E24</f>
-        <v>1140800</v>
+        <v>308200</v>
       </c>
       <c r="H24" s="16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="14.65" x14ac:dyDescent="0.45">
       <c r="A25" s="6"/>
       <c r="B25" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C25" s="10">
-        <v>680000</v>
+        <v>483000</v>
       </c>
       <c r="D25" s="14">
         <f>C25/SUM($C$23:$C$27)</f>
-        <v>0.128060263653484</v>
+        <v>0.22486033519553073</v>
       </c>
       <c r="E25" s="15">
         <v>0.8</v>
       </c>
       <c r="F25" s="11">
         <f>C25*E25</f>
-        <v>544000</v>
+        <v>386400</v>
       </c>
       <c r="H25" s="16" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="14.65" x14ac:dyDescent="0.45">
       <c r="A26" s="7"/>
       <c r="B26" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C26" s="12">
-        <v>420000</v>
+        <v>520000</v>
       </c>
       <c r="D26" s="17">
         <f>C26/SUM($C$23:$C$27)</f>
-        <v>7.909604519774012E-2</v>
+        <v>0.24208566108007448</v>
       </c>
       <c r="E26" s="18">
         <v>0.55000000000000004</v>
       </c>
       <c r="F26" s="13">
         <f>C26*E26</f>
-        <v>231000.00000000003</v>
+        <v>286000</v>
       </c>
       <c r="H26" s="16" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="14.65" x14ac:dyDescent="0.45">
       <c r="A27" s="6"/>
       <c r="B27" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C27" s="10">
         <v>290000</v>
       </c>
       <c r="D27" s="14">
         <f>C27/SUM($C$23:$C$27)</f>
-        <v>5.4613935969868174E-2</v>
+        <v>0.13500931098696461</v>
       </c>
       <c r="E27" s="15">
         <v>0.25</v>
@@ -2291,17 +2277,17 @@
         <v>72500</v>
       </c>
       <c r="H27" s="19" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="14.65" x14ac:dyDescent="0.3">
       <c r="A28" s="20"/>
       <c r="B28" s="20" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C28" s="21">
         <f>SUM(C23:C27)</f>
-        <v>5310000</v>
+        <v>2148000</v>
       </c>
       <c r="D28" s="22">
         <v>1</v>
@@ -2309,37 +2295,37 @@
       <c r="E28" s="20"/>
       <c r="F28" s="21">
         <f>SUM(F23:F27)</f>
-        <v>4614700</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="38" t="s">
-        <v>86</v>
-      </c>
-      <c r="B30" s="36"/>
-      <c r="C30" s="36"/>
-      <c r="D30" s="36"/>
-      <c r="E30" s="36"/>
-      <c r="F30" s="36"/>
-      <c r="G30" s="36"/>
-      <c r="H30" s="36"/>
-      <c r="I30" s="36"/>
+        <v>1562700</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="90" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="B30" s="37"/>
+      <c r="C30" s="37"/>
+      <c r="D30" s="37"/>
+      <c r="E30" s="37"/>
+      <c r="F30" s="37"/>
+      <c r="G30" s="37"/>
+      <c r="H30" s="37"/>
+      <c r="I30" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
     <mergeCell ref="A30:I30"/>
     <mergeCell ref="A21:I21"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
-  <conditionalFormatting sqref="D23:D27">
-    <cfRule type="cellIs" dxfId="8" priority="2" operator="greaterThan">
-      <formula>0.4</formula>
+  <conditionalFormatting sqref="C23:H27">
+    <cfRule type="expression" dxfId="9" priority="2">
+      <formula>$E23&lt;0.6</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8:E19">
-    <cfRule type="cellIs" dxfId="7" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="8" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2353,9 +2339,9 @@
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
-    <col min="2" max="2" width="13.796875" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="18.9296875" customWidth="1"/>
+    <col min="4" max="4" width="15.59765625" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
     <col min="6" max="6" width="4" customWidth="1"/>
     <col min="7" max="7" width="16" customWidth="1"/>
@@ -2363,42 +2349,44 @@
     <col min="10" max="10" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="39" t="s">
-        <v>87</v>
-      </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-    </row>
-    <row r="2" spans="1:10" ht="31.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="40" t="s">
+    <row r="1" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="38" t="s">
         <v>88</v>
       </c>
-      <c r="B2" s="40"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="40"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="39" t="s">
+        <v>89</v>
+      </c>
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
+      <c r="I2" s="37"/>
+      <c r="J2" s="37"/>
     </row>
     <row r="4" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C4" s="8">
         <f>SUM(C8:C19)</f>
         <v>11695000</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E4" s="23">
         <f>SUM(C8:C10)/SUM(C8:C19)</f>
@@ -2406,14 +2394,14 @@
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H4" s="23">
         <f>MAX(C8:C19)/SUM(C8:C19)</f>
         <v>0.24454895254382214</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J4" s="24" t="str">
         <f>IF(H4&gt;0.4,"⚠️ 危险：单一客户超 40%",IF(H4&gt;0.25,"注意：偏高","健康"))</f>
@@ -2423,35 +2411,35 @@
     <row r="7" spans="1:10" ht="26" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5"/>
       <c r="B7" s="5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F7" s="5"/>
       <c r="G7" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="14.65" x14ac:dyDescent="0.45">
       <c r="A8" s="6"/>
       <c r="B8" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C8" s="10">
         <v>2860000</v>
@@ -2465,14 +2453,14 @@
         <v>0.24454895254382214</v>
       </c>
       <c r="G8" s="25" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H8" s="26">
-        <v>5820000</v>
+        <v>5450000</v>
       </c>
       <c r="I8" s="27">
         <f>H8/SUM($H$8:$H$10)</f>
-        <v>0.46007905138339922</v>
+        <v>0.45153272576636289</v>
       </c>
       <c r="J8" s="27">
         <v>0.312</v>
@@ -2481,7 +2469,7 @@
     <row r="9" spans="1:10" ht="14.65" x14ac:dyDescent="0.45">
       <c r="A9" s="7"/>
       <c r="B9" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C9" s="12">
         <v>2140000</v>
@@ -2495,14 +2483,14 @@
         <v>0.42753313381787089</v>
       </c>
       <c r="G9" s="25" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H9" s="26">
-        <v>3980000</v>
+        <v>3850000</v>
       </c>
       <c r="I9" s="27">
         <f>H9/SUM($H$8:$H$10)</f>
-        <v>0.31462450592885377</v>
+        <v>0.31897265948632975</v>
       </c>
       <c r="J9" s="27">
         <v>0.248</v>
@@ -2511,7 +2499,7 @@
     <row r="10" spans="1:10" ht="14.65" x14ac:dyDescent="0.45">
       <c r="A10" s="6"/>
       <c r="B10" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C10" s="10">
         <v>1680000</v>
@@ -2525,14 +2513,14 @@
         <v>0.57118426678067546</v>
       </c>
       <c r="G10" s="25" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H10" s="26">
-        <v>2850000</v>
+        <v>2770000</v>
       </c>
       <c r="I10" s="27">
         <f>H10/SUM($H$8:$H$10)</f>
-        <v>0.22529644268774704</v>
+        <v>0.22949461474730737</v>
       </c>
       <c r="J10" s="27">
         <v>0.19600000000000001</v>
@@ -2541,7 +2529,7 @@
     <row r="11" spans="1:10" ht="13.9" x14ac:dyDescent="0.3">
       <c r="A11" s="7"/>
       <c r="B11" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C11" s="12">
         <v>1250000</v>
@@ -2558,7 +2546,7 @@
     <row r="12" spans="1:10" ht="13.9" x14ac:dyDescent="0.3">
       <c r="A12" s="6"/>
       <c r="B12" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C12" s="10">
         <v>980000</v>
@@ -2575,7 +2563,7 @@
     <row r="13" spans="1:10" ht="13.9" x14ac:dyDescent="0.3">
       <c r="A13" s="7"/>
       <c r="B13" s="7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C13" s="12">
         <v>760000</v>
@@ -2592,7 +2580,7 @@
     <row r="14" spans="1:10" ht="13.9" x14ac:dyDescent="0.3">
       <c r="A14" s="6"/>
       <c r="B14" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C14" s="10">
         <v>620000</v>
@@ -2609,7 +2597,7 @@
     <row r="15" spans="1:10" ht="13.9" x14ac:dyDescent="0.3">
       <c r="A15" s="7"/>
       <c r="B15" s="7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C15" s="12">
         <v>480000</v>
@@ -2626,7 +2614,7 @@
     <row r="16" spans="1:10" ht="13.9" x14ac:dyDescent="0.3">
       <c r="A16" s="6"/>
       <c r="B16" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C16" s="10">
         <v>390000</v>
@@ -2643,7 +2631,7 @@
     <row r="17" spans="1:10" ht="13.9" x14ac:dyDescent="0.3">
       <c r="A17" s="7"/>
       <c r="B17" s="7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C17" s="12">
         <v>260000</v>
@@ -2660,7 +2648,7 @@
     <row r="18" spans="1:10" ht="13.9" x14ac:dyDescent="0.3">
       <c r="A18" s="6"/>
       <c r="B18" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C18" s="10">
         <v>180000</v>
@@ -2677,7 +2665,7 @@
     <row r="19" spans="1:10" ht="13.9" x14ac:dyDescent="0.3">
       <c r="A19" s="7"/>
       <c r="B19" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C19" s="12">
         <v>95000</v>
@@ -2692,32 +2680,32 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="42" t="s">
-        <v>114</v>
-      </c>
-      <c r="B21" s="42"/>
-      <c r="C21" s="42"/>
-      <c r="D21" s="42"/>
-      <c r="E21" s="42"/>
-      <c r="F21" s="42"/>
-      <c r="G21" s="42"/>
-      <c r="H21" s="42"/>
-      <c r="I21" s="42"/>
-      <c r="J21" s="42"/>
+      <c r="A21" s="43" t="s">
+        <v>115</v>
+      </c>
+      <c r="B21" s="43"/>
+      <c r="C21" s="43"/>
+      <c r="D21" s="43"/>
+      <c r="E21" s="43"/>
+      <c r="F21" s="43"/>
+      <c r="G21" s="43"/>
+      <c r="H21" s="43"/>
+      <c r="I21" s="43"/>
+      <c r="J21" s="43"/>
     </row>
     <row r="22" spans="1:10" ht="26" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5"/>
       <c r="B22" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F22" s="5"/>
       <c r="G22" s="5"/>
@@ -2728,7 +2716,7 @@
     <row r="23" spans="1:10" ht="13.9" x14ac:dyDescent="0.3">
       <c r="A23" s="6"/>
       <c r="B23" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C23" s="10">
         <v>4260000</v>
@@ -2744,7 +2732,7 @@
     <row r="24" spans="1:10" ht="13.9" x14ac:dyDescent="0.3">
       <c r="A24" s="7"/>
       <c r="B24" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C24" s="12">
         <v>3150000</v>
@@ -2760,7 +2748,7 @@
     <row r="25" spans="1:10" ht="13.9" x14ac:dyDescent="0.3">
       <c r="A25" s="6"/>
       <c r="B25" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C25" s="10">
         <v>2380000</v>
@@ -2776,7 +2764,7 @@
     <row r="26" spans="1:10" ht="13.9" x14ac:dyDescent="0.3">
       <c r="A26" s="7"/>
       <c r="B26" s="7" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C26" s="12">
         <v>1420000</v>
@@ -2792,7 +2780,7 @@
     <row r="27" spans="1:10" ht="13.9" x14ac:dyDescent="0.3">
       <c r="A27" s="6"/>
       <c r="B27" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C27" s="10">
         <v>860000</v>
@@ -2805,35 +2793,38 @@
         <v>-0.12</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="38" t="s">
-        <v>122</v>
-      </c>
-      <c r="B29" s="36"/>
-      <c r="C29" s="36"/>
-      <c r="D29" s="36"/>
-      <c r="E29" s="36"/>
-      <c r="F29" s="36"/>
-      <c r="G29" s="36"/>
-      <c r="H29" s="36"/>
-      <c r="I29" s="36"/>
-      <c r="J29" s="36"/>
+    <row r="29" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="41" t="s">
+        <v>123</v>
+      </c>
+      <c r="B29" s="37"/>
+      <c r="C29" s="37"/>
+      <c r="D29" s="37"/>
+      <c r="E29" s="37"/>
+      <c r="F29" s="37"/>
+      <c r="G29" s="37"/>
+      <c r="H29" s="37"/>
+      <c r="I29" s="37"/>
+      <c r="J29" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="A1:J1"/>
     <mergeCell ref="A29:J29"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A2:J2"/>
     <mergeCell ref="A21:J21"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <conditionalFormatting sqref="D8:D19">
-    <cfRule type="cellIs" dxfId="6" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="greaterThan">
       <formula>0.15</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E23:E27">
-    <cfRule type="cellIs" dxfId="5" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="5" priority="3" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2849,60 +2840,62 @@
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="16.1328125" customWidth="1"/>
+    <col min="4" max="4" width="15.3984375" customWidth="1"/>
     <col min="5" max="7" width="14" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="31.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="39" t="s">
-        <v>123</v>
-      </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-    </row>
-    <row r="2" spans="1:9" ht="29.65" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="40" t="s">
+    <row r="1" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="38" t="s">
         <v>124</v>
       </c>
-      <c r="B2" s="40"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="40"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" s="39" t="s">
+        <v>125</v>
+      </c>
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
+      <c r="I2" s="37"/>
     </row>
     <row r="4" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C4" s="23">
         <v>0.25</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E4" s="30">
         <f>COUNTIF(G8:G17,"&lt;0.25")</f>
         <v>7</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G4" s="23">
         <f>IF(SUM(C8:C17)=0,0,SUM(F8:F17)/SUM(C8:C17))</f>
         <v>0.22239641657334827</v>
       </c>
-      <c r="H4" s="4"/>
+      <c r="H4" s="2" t="s">
+        <v>239</v>
+      </c>
       <c r="I4" s="24" t="str">
         <f>IF(E4=0,"全部达标","⚠️ 有 "&amp;E4&amp;" 个项目低于底线")</f>
         <v>⚠️ 有 7 个项目低于底线</v>
@@ -2911,34 +2904,34 @@
     <row r="7" spans="1:9" ht="26" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5"/>
       <c r="B7" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="14.65" x14ac:dyDescent="0.45">
       <c r="A8" s="6"/>
       <c r="B8" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C8" s="10">
         <v>1860000</v>
@@ -2969,7 +2962,7 @@
     <row r="9" spans="1:9" ht="14.65" x14ac:dyDescent="0.45">
       <c r="A9" s="7"/>
       <c r="B9" s="7" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C9" s="12">
         <v>1420000</v>
@@ -3000,7 +2993,7 @@
     <row r="10" spans="1:9" ht="14.65" x14ac:dyDescent="0.45">
       <c r="A10" s="6"/>
       <c r="B10" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C10" s="10">
         <v>1180000</v>
@@ -3031,7 +3024,7 @@
     <row r="11" spans="1:9" ht="14.65" x14ac:dyDescent="0.45">
       <c r="A11" s="7"/>
       <c r="B11" s="7" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C11" s="12">
         <v>960000</v>
@@ -3062,7 +3055,7 @@
     <row r="12" spans="1:9" ht="14.65" x14ac:dyDescent="0.45">
       <c r="A12" s="6"/>
       <c r="B12" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C12" s="10">
         <v>880000</v>
@@ -3093,7 +3086,7 @@
     <row r="13" spans="1:9" ht="14.65" x14ac:dyDescent="0.45">
       <c r="A13" s="7"/>
       <c r="B13" s="7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C13" s="12">
         <v>760000</v>
@@ -3124,7 +3117,7 @@
     <row r="14" spans="1:9" ht="14.65" x14ac:dyDescent="0.45">
       <c r="A14" s="6"/>
       <c r="B14" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C14" s="10">
         <v>640000</v>
@@ -3155,7 +3148,7 @@
     <row r="15" spans="1:9" ht="14.65" x14ac:dyDescent="0.45">
       <c r="A15" s="7"/>
       <c r="B15" s="7" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C15" s="12">
         <v>520000</v>
@@ -3186,7 +3179,7 @@
     <row r="16" spans="1:9" ht="14.65" x14ac:dyDescent="0.45">
       <c r="A16" s="6"/>
       <c r="B16" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C16" s="10">
         <v>430000</v>
@@ -3217,7 +3210,7 @@
     <row r="17" spans="1:9" ht="14.65" x14ac:dyDescent="0.45">
       <c r="A17" s="7"/>
       <c r="B17" s="7" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C17" s="12">
         <v>280000</v>
@@ -3248,7 +3241,7 @@
     <row r="18" spans="1:9" ht="14.65" x14ac:dyDescent="0.3">
       <c r="A18" s="20"/>
       <c r="B18" s="20" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C18" s="21">
         <f>SUM(C8:C17)</f>
@@ -3271,23 +3264,23 @@
         <v>0.22239641657334827</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="38" t="s">
-        <v>145</v>
-      </c>
-      <c r="B20" s="36"/>
-      <c r="C20" s="36"/>
-      <c r="D20" s="36"/>
-      <c r="E20" s="36"/>
-      <c r="F20" s="36"/>
-      <c r="G20" s="36"/>
-      <c r="H20" s="36"/>
-      <c r="I20" s="36"/>
+    <row r="20" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="41" t="s">
+        <v>146</v>
+      </c>
+      <c r="B20" s="37"/>
+      <c r="C20" s="37"/>
+      <c r="D20" s="37"/>
+      <c r="E20" s="37"/>
+      <c r="F20" s="37"/>
+      <c r="G20" s="37"/>
+      <c r="H20" s="37"/>
+      <c r="I20" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A20:I20"/>
-    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
@@ -3302,114 +3295,112 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="5" width="16" customWidth="1"/>
     <col min="6" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="19.73046875" customWidth="1"/>
-    <col min="10" max="10" width="16.19921875" customWidth="1"/>
+    <col min="9" max="9" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="55.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="39" t="s">
-        <v>146</v>
-      </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-    </row>
-    <row r="2" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="40" t="s">
+    <row r="1" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="38" t="s">
         <v>147</v>
       </c>
-      <c r="B2" s="40"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="40"/>
-    </row>
-    <row r="4" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" s="39" t="s">
+        <v>148</v>
+      </c>
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
+      <c r="I2" s="37"/>
+    </row>
+    <row r="4" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C4" s="8">
         <f>SUM(C8:C22)</f>
         <v>9090000</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E4" s="8">
         <f>SUM(G8:G22)</f>
         <v>4881000</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G4" s="23">
         <f>IF(C4=0,0,E4/C4)</f>
         <v>0.53696369636963692</v>
       </c>
-      <c r="H4" s="4"/>
-      <c r="I4" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="J4" s="8">
+      <c r="H4" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="I4" s="8">
         <f>SUMIF(I8:I22,"2026-Q4",G8:G22)</f>
         <v>4566500</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="26" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="26" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5"/>
       <c r="B7" s="5" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>93</v>
+        <v>154</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="13.9" x14ac:dyDescent="0.3">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="13.9" x14ac:dyDescent="0.3">
       <c r="A8" s="6"/>
       <c r="B8" s="6" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C8" s="10">
         <v>1680000</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F8" s="15">
         <v>0.8</v>
@@ -3422,22 +3413,22 @@
         <v>42</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="13.9" x14ac:dyDescent="0.3">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="13.9" x14ac:dyDescent="0.3">
       <c r="A9" s="7"/>
       <c r="B9" s="7" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C9" s="12">
         <v>1240000</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F9" s="18">
         <v>0.5</v>
@@ -3450,22 +3441,22 @@
         <v>18</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="13.9" x14ac:dyDescent="0.3">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="13.9" x14ac:dyDescent="0.3">
       <c r="A10" s="6"/>
       <c r="B10" s="6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C10" s="10">
         <v>980000</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F10" s="15">
         <v>0.8</v>
@@ -3478,22 +3469,22 @@
         <v>55</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="13.9" x14ac:dyDescent="0.3">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="13.9" x14ac:dyDescent="0.3">
       <c r="A11" s="7"/>
       <c r="B11" s="7" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C11" s="12">
         <v>860000</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F11" s="18">
         <v>0.35</v>
@@ -3506,22 +3497,22 @@
         <v>12</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="13.9" x14ac:dyDescent="0.3">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="13.9" x14ac:dyDescent="0.3">
       <c r="A12" s="6"/>
       <c r="B12" s="6" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C12" s="10">
         <v>720000</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F12" s="15">
         <v>0.5</v>
@@ -3534,22 +3525,22 @@
         <v>31</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="13.9" x14ac:dyDescent="0.3">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="13.9" x14ac:dyDescent="0.3">
       <c r="A13" s="7"/>
       <c r="B13" s="7" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C13" s="12">
         <v>640000</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F13" s="18">
         <v>0.15</v>
@@ -3562,22 +3553,22 @@
         <v>8</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="13.9" x14ac:dyDescent="0.3">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="13.9" x14ac:dyDescent="0.3">
       <c r="A14" s="6"/>
       <c r="B14" s="6" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C14" s="10">
         <v>580000</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F14" s="15">
         <v>0.35</v>
@@ -3590,22 +3581,22 @@
         <v>24</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="13.9" x14ac:dyDescent="0.3">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="13.9" x14ac:dyDescent="0.3">
       <c r="A15" s="7"/>
       <c r="B15" s="7" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C15" s="12">
         <v>490000</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F15" s="18">
         <v>0.5</v>
@@ -3618,22 +3609,22 @@
         <v>47</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="13.9" x14ac:dyDescent="0.3">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="13.9" x14ac:dyDescent="0.3">
       <c r="A16" s="6"/>
       <c r="B16" s="6" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C16" s="10">
         <v>430000</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="F16" s="15">
         <v>0.95</v>
@@ -3646,22 +3637,22 @@
         <v>6</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="13.9" x14ac:dyDescent="0.3">
       <c r="A17" s="7"/>
       <c r="B17" s="7" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C17" s="12">
         <v>380000</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F17" s="18">
         <v>0.15</v>
@@ -3674,22 +3665,22 @@
         <v>5</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="13.9" x14ac:dyDescent="0.3">
       <c r="A18" s="6"/>
       <c r="B18" s="6" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C18" s="10">
         <v>320000</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F18" s="15">
         <v>0.35</v>
@@ -3702,22 +3693,22 @@
         <v>19</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="13.9" x14ac:dyDescent="0.3">
       <c r="A19" s="7"/>
       <c r="B19" s="7" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C19" s="12">
         <v>260000</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F19" s="18">
         <v>0.5</v>
@@ -3730,22 +3721,22 @@
         <v>38</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="13.9" x14ac:dyDescent="0.3">
       <c r="A20" s="6"/>
       <c r="B20" s="6" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C20" s="10">
         <v>210000</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F20" s="15">
         <v>0.15</v>
@@ -3758,22 +3749,22 @@
         <v>3</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="13.9" x14ac:dyDescent="0.3">
       <c r="A21" s="7"/>
       <c r="B21" s="7" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C21" s="12">
         <v>180000</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="F21" s="18">
         <v>0.95</v>
@@ -3786,22 +3777,22 @@
         <v>4</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="13.9" x14ac:dyDescent="0.3">
       <c r="A22" s="6"/>
       <c r="B22" s="6" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C22" s="10">
         <v>120000</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F22" s="15">
         <v>0.15</v>
@@ -3814,26 +3805,26 @@
         <v>2</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="38" t="s">
-        <v>183</v>
-      </c>
-      <c r="B25" s="36"/>
-      <c r="C25" s="36"/>
-      <c r="D25" s="36"/>
-      <c r="E25" s="36"/>
-      <c r="F25" s="36"/>
-      <c r="G25" s="36"/>
-      <c r="H25" s="36"/>
-      <c r="I25" s="36"/>
+        <v>171</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="41" t="s">
+        <v>185</v>
+      </c>
+      <c r="B25" s="37"/>
+      <c r="C25" s="37"/>
+      <c r="D25" s="37"/>
+      <c r="E25" s="37"/>
+      <c r="F25" s="37"/>
+      <c r="G25" s="37"/>
+      <c r="H25" s="37"/>
+      <c r="I25" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A25:I25"/>
-    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
@@ -3866,60 +3857,62 @@
     <col min="10" max="10" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="57.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="39" t="s">
-        <v>184</v>
-      </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-    </row>
-    <row r="2" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="40" t="s">
-        <v>185</v>
-      </c>
-      <c r="B2" s="40"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="40"/>
+    <row r="1" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="38" t="s">
+        <v>186</v>
+      </c>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="39" t="s">
+        <v>187</v>
+      </c>
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
+      <c r="I2" s="37"/>
+      <c r="J2" s="37"/>
     </row>
     <row r="4" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C4" s="30">
         <f>SUM(C8:C12)</f>
         <v>26</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E4" s="8">
         <f>D13/C4</f>
         <v>464230.76923076925</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="G4" s="23">
         <f>E13/D13</f>
         <v>0.87075393537696766</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I4" s="30">
-        <f>ROUND(AVERAGE(H8:H12),0)</f>
-        <v>71</v>
+        <f>H13</f>
+        <v>65</v>
       </c>
       <c r="J4" s="24" t="str">
         <f>IF(I4&gt;60,"⚠️ 回款周期偏长","健康")</f>
@@ -3929,255 +3922,255 @@
     <row r="7" spans="1:10" ht="26" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5"/>
       <c r="B7" s="5" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="13.9" x14ac:dyDescent="0.3">
-      <c r="A8" s="49"/>
-      <c r="B8" s="49" t="s">
-        <v>198</v>
-      </c>
-      <c r="C8" s="45">
+      <c r="A8" s="6"/>
+      <c r="B8" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="C8" s="33">
         <v>8</v>
       </c>
-      <c r="D8" s="50">
+      <c r="D8" s="10">
         <v>4260000</v>
       </c>
-      <c r="E8" s="50">
+      <c r="E8" s="10">
         <v>3820000</v>
       </c>
-      <c r="F8" s="43">
+      <c r="F8" s="14">
         <f t="shared" ref="F8:F13" si="0">E8/D8</f>
         <v>0.89671361502347413</v>
       </c>
-      <c r="G8" s="50">
+      <c r="G8" s="11">
         <f t="shared" ref="G8:G13" si="1">D8/C8</f>
         <v>532500</v>
       </c>
-      <c r="H8" s="45">
+      <c r="H8" s="33">
         <v>58</v>
       </c>
-      <c r="I8" s="50">
+      <c r="I8" s="10">
         <v>320000</v>
       </c>
-      <c r="J8" s="43">
+      <c r="J8" s="14">
         <f t="shared" ref="J8:J13" si="2">I8/D8</f>
         <v>7.5117370892018781E-2</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="13.9" x14ac:dyDescent="0.3">
-      <c r="A9" s="51"/>
-      <c r="B9" s="51" t="s">
-        <v>199</v>
-      </c>
-      <c r="C9" s="46">
+      <c r="A9" s="7"/>
+      <c r="B9" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="C9" s="34">
         <v>6</v>
       </c>
-      <c r="D9" s="52">
+      <c r="D9" s="12">
         <v>3150000</v>
       </c>
-      <c r="E9" s="52">
+      <c r="E9" s="12">
         <v>2640000</v>
       </c>
-      <c r="F9" s="44">
+      <c r="F9" s="17">
         <f t="shared" si="0"/>
         <v>0.83809523809523812</v>
       </c>
-      <c r="G9" s="52">
+      <c r="G9" s="13">
         <f t="shared" si="1"/>
         <v>525000</v>
       </c>
-      <c r="H9" s="46">
+      <c r="H9" s="34">
         <v>72</v>
       </c>
-      <c r="I9" s="52">
+      <c r="I9" s="12">
         <v>410000</v>
       </c>
-      <c r="J9" s="44">
+      <c r="J9" s="17">
         <f t="shared" si="2"/>
         <v>0.13015873015873017</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="13.9" x14ac:dyDescent="0.3">
-      <c r="A10" s="49"/>
-      <c r="B10" s="49" t="s">
-        <v>200</v>
-      </c>
-      <c r="C10" s="45">
+      <c r="A10" s="6"/>
+      <c r="B10" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="C10" s="33">
         <v>5</v>
       </c>
-      <c r="D10" s="50">
+      <c r="D10" s="10">
         <v>2380000</v>
       </c>
-      <c r="E10" s="50">
+      <c r="E10" s="10">
         <v>2180000</v>
       </c>
-      <c r="F10" s="43">
+      <c r="F10" s="14">
         <f t="shared" si="0"/>
         <v>0.91596638655462181</v>
       </c>
-      <c r="G10" s="50">
+      <c r="G10" s="11">
         <f t="shared" si="1"/>
         <v>476000</v>
       </c>
-      <c r="H10" s="45">
+      <c r="H10" s="33">
         <v>46</v>
       </c>
-      <c r="I10" s="50">
+      <c r="I10" s="10">
         <v>145000</v>
       </c>
-      <c r="J10" s="43">
+      <c r="J10" s="14">
         <f t="shared" si="2"/>
         <v>6.0924369747899158E-2</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="13.9" x14ac:dyDescent="0.3">
-      <c r="A11" s="51"/>
-      <c r="B11" s="51" t="s">
-        <v>201</v>
-      </c>
-      <c r="C11" s="46">
+      <c r="A11" s="7"/>
+      <c r="B11" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="C11" s="34">
         <v>4</v>
       </c>
-      <c r="D11" s="52">
+      <c r="D11" s="12">
         <v>1420000</v>
       </c>
-      <c r="E11" s="52">
+      <c r="E11" s="12">
         <v>1180000</v>
       </c>
-      <c r="F11" s="44">
+      <c r="F11" s="17">
         <f t="shared" si="0"/>
         <v>0.83098591549295775</v>
       </c>
-      <c r="G11" s="52">
+      <c r="G11" s="13">
         <f t="shared" si="1"/>
         <v>355000</v>
       </c>
-      <c r="H11" s="46">
+      <c r="H11" s="34">
         <v>83</v>
       </c>
-      <c r="I11" s="52">
+      <c r="I11" s="12">
         <v>268000</v>
       </c>
-      <c r="J11" s="44">
+      <c r="J11" s="17">
         <f t="shared" si="2"/>
         <v>0.18873239436619718</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="13.9" x14ac:dyDescent="0.3">
-      <c r="A12" s="49"/>
-      <c r="B12" s="49" t="s">
-        <v>202</v>
-      </c>
-      <c r="C12" s="45">
+      <c r="A12" s="6"/>
+      <c r="B12" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="C12" s="33">
         <v>3</v>
       </c>
-      <c r="D12" s="50">
+      <c r="D12" s="10">
         <v>860000</v>
       </c>
-      <c r="E12" s="50">
+      <c r="E12" s="10">
         <v>690000</v>
       </c>
-      <c r="F12" s="43">
+      <c r="F12" s="14">
         <f t="shared" si="0"/>
         <v>0.80232558139534882</v>
       </c>
-      <c r="G12" s="50">
+      <c r="G12" s="11">
         <f t="shared" si="1"/>
         <v>286666.66666666669</v>
       </c>
-      <c r="H12" s="45">
+      <c r="H12" s="33">
         <v>95</v>
       </c>
-      <c r="I12" s="50">
-        <v>224000</v>
-      </c>
-      <c r="J12" s="43">
+      <c r="I12" s="10">
+        <v>150000</v>
+      </c>
+      <c r="J12" s="14">
         <f t="shared" si="2"/>
-        <v>0.26046511627906976</v>
+        <v>0.1744186046511628</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="14.65" x14ac:dyDescent="0.3">
-      <c r="A13" s="53"/>
-      <c r="B13" s="53" t="s">
-        <v>85</v>
-      </c>
-      <c r="C13" s="47">
+      <c r="A13" s="20"/>
+      <c r="B13" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="C13" s="35">
         <f>SUM(C8:C12)</f>
         <v>26</v>
       </c>
-      <c r="D13" s="54">
+      <c r="D13" s="21">
         <f>SUM(D8:D12)</f>
         <v>12070000</v>
       </c>
-      <c r="E13" s="54">
+      <c r="E13" s="21">
         <f>SUM(E8:E12)</f>
         <v>10510000</v>
       </c>
-      <c r="F13" s="48">
+      <c r="F13" s="32">
         <f t="shared" si="0"/>
         <v>0.87075393537696766</v>
       </c>
-      <c r="G13" s="54">
+      <c r="G13" s="21">
         <f t="shared" si="1"/>
         <v>464230.76923076925</v>
       </c>
-      <c r="H13" s="47">
-        <f>ROUND(AVERAGE(H8:H12),0)</f>
-        <v>71</v>
-      </c>
-      <c r="I13" s="54">
+      <c r="H13" s="35">
+        <f>ROUND(SUMPRODUCT(D8:D12,H8:H12)/SUM(D8:D12),0)</f>
+        <v>65</v>
+      </c>
+      <c r="I13" s="21">
         <f>SUM(I8:I12)</f>
-        <v>1367000</v>
-      </c>
-      <c r="J13" s="48">
+        <v>1293000</v>
+      </c>
+      <c r="J13" s="32">
         <f t="shared" si="2"/>
-        <v>0.11325600662800331</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="38" t="s">
-        <v>203</v>
-      </c>
-      <c r="B15" s="36"/>
-      <c r="C15" s="36"/>
-      <c r="D15" s="36"/>
-      <c r="E15" s="36"/>
-      <c r="F15" s="36"/>
-      <c r="G15" s="36"/>
-      <c r="H15" s="36"/>
-      <c r="I15" s="36"/>
-      <c r="J15" s="36"/>
+        <v>0.10712510356255178</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="108" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="41" t="s">
+        <v>205</v>
+      </c>
+      <c r="B15" s="37"/>
+      <c r="C15" s="37"/>
+      <c r="D15" s="37"/>
+      <c r="E15" s="37"/>
+      <c r="F15" s="37"/>
+      <c r="G15" s="37"/>
+      <c r="H15" s="37"/>
+      <c r="I15" s="37"/>
+      <c r="J15" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A1:J1"/>
     <mergeCell ref="A15:J15"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A2:J2"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <conditionalFormatting sqref="F8:F12">
@@ -4196,260 +4189,253 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="53.33203125" customWidth="1"/>
-    <col min="4" max="4" width="34" customWidth="1"/>
+    <col min="3" max="4" width="34" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="43.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="39" t="s">
-        <v>204</v>
-      </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-    </row>
-    <row r="2" spans="1:9" ht="22.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="40" t="s">
-        <v>205</v>
-      </c>
-      <c r="B2" s="40"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="40"/>
-    </row>
-    <row r="4" spans="1:9" ht="26" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="38" t="s">
+        <v>206</v>
+      </c>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="39" t="s">
+        <v>207</v>
+      </c>
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+    </row>
+    <row r="4" spans="1:6" ht="26" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5"/>
       <c r="B4" s="5" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="6"/>
       <c r="B5" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="D5" s="3" t="s">
         <v>213</v>
       </c>
+      <c r="C5" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>215</v>
+      </c>
       <c r="E5" s="6" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="F5" s="6"/>
     </row>
-    <row r="6" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6"/>
       <c r="B6" s="6"/>
-      <c r="C6" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="D6" s="3"/>
+      <c r="C6" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="D6" s="6"/>
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
     </row>
-    <row r="7" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6"/>
       <c r="B7" s="6"/>
-      <c r="C7" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="D7" s="3"/>
+      <c r="C7" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="D7" s="6"/>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
     </row>
-    <row r="8" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="6"/>
       <c r="B8" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D8" s="3" t="s">
         <v>219</v>
       </c>
+      <c r="C8" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>221</v>
+      </c>
       <c r="E8" s="6" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="F8" s="6"/>
     </row>
-    <row r="9" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
-      <c r="C9" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="D9" s="3"/>
+      <c r="C9" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="D9" s="6"/>
       <c r="E9" s="6"/>
       <c r="F9" s="6"/>
     </row>
-    <row r="10" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="6"/>
       <c r="B10" s="6"/>
-      <c r="C10" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="D10" s="3"/>
+      <c r="C10" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="D10" s="6"/>
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
     </row>
-    <row r="11" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="6"/>
       <c r="B11" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="D11" s="3" t="s">
         <v>224</v>
       </c>
+      <c r="C11" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>226</v>
+      </c>
       <c r="E11" s="6" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="F11" s="6"/>
     </row>
-    <row r="12" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="6"/>
       <c r="B12" s="6"/>
-      <c r="C12" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="D12" s="3"/>
+      <c r="C12" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="D12" s="6"/>
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
     </row>
-    <row r="13" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6"/>
       <c r="B13" s="6"/>
-      <c r="C13" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="D13" s="3"/>
+      <c r="C13" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="D13" s="6"/>
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
     </row>
-    <row r="14" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="6"/>
       <c r="B14" s="6" t="s">
-        <v>227</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="D14" s="3" t="s">
         <v>229</v>
       </c>
+      <c r="C14" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>231</v>
+      </c>
       <c r="E14" s="6" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="F14" s="6"/>
     </row>
-    <row r="15" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
-      <c r="C15" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="D15" s="3"/>
+      <c r="C15" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="D15" s="6"/>
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
     </row>
-    <row r="16" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="6"/>
       <c r="B16" s="6"/>
-      <c r="C16" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="D16" s="3"/>
+      <c r="C16" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="D16" s="6"/>
       <c r="E16" s="6"/>
       <c r="F16" s="6"/>
     </row>
     <row r="18" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="41" t="s">
-        <v>232</v>
-      </c>
-      <c r="B18" s="41"/>
-      <c r="C18" s="41"/>
-      <c r="D18" s="41"/>
-      <c r="E18" s="41"/>
-      <c r="F18" s="41"/>
+      <c r="A18" s="42" t="s">
+        <v>234</v>
+      </c>
+      <c r="B18" s="42"/>
+      <c r="C18" s="42"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="42"/>
+      <c r="F18" s="42"/>
     </row>
     <row r="19" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="35" t="s">
-        <v>233</v>
-      </c>
-      <c r="C19" s="36"/>
-      <c r="D19" s="36"/>
-      <c r="E19" s="36"/>
-      <c r="F19" s="36"/>
+      <c r="B19" s="36" t="s">
+        <v>235</v>
+      </c>
+      <c r="C19" s="37"/>
+      <c r="D19" s="37"/>
+      <c r="E19" s="37"/>
+      <c r="F19" s="37"/>
     </row>
     <row r="20" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="35" t="s">
-        <v>234</v>
-      </c>
-      <c r="C20" s="36"/>
-      <c r="D20" s="36"/>
-      <c r="E20" s="36"/>
-      <c r="F20" s="36"/>
+      <c r="B20" s="36" t="s">
+        <v>236</v>
+      </c>
+      <c r="C20" s="37"/>
+      <c r="D20" s="37"/>
+      <c r="E20" s="37"/>
+      <c r="F20" s="37"/>
     </row>
     <row r="21" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="35" t="s">
-        <v>235</v>
-      </c>
-      <c r="C21" s="36"/>
-      <c r="D21" s="36"/>
-      <c r="E21" s="36"/>
-      <c r="F21" s="36"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B23" s="37" t="s">
-        <v>236</v>
-      </c>
-      <c r="C23" s="36"/>
-      <c r="D23" s="36"/>
-      <c r="E23" s="36"/>
-      <c r="F23" s="36"/>
+      <c r="B21" s="36" t="s">
+        <v>237</v>
+      </c>
+      <c r="C21" s="37"/>
+      <c r="D21" s="37"/>
+      <c r="E21" s="37"/>
+      <c r="F21" s="37"/>
+    </row>
+    <row r="23" spans="1:6" ht="26.65" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="40" t="s">
+        <v>238</v>
+      </c>
+      <c r="C23" s="37"/>
+      <c r="D23" s="37"/>
+      <c r="E23" s="37"/>
+      <c r="F23" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="B23:F23"/>
+    <mergeCell ref="A18:F18"/>
     <mergeCell ref="B21:F21"/>
+    <mergeCell ref="A2:F2"/>
     <mergeCell ref="B20:F20"/>
-    <mergeCell ref="B23:F23"/>
+    <mergeCell ref="A1:F1"/>
     <mergeCell ref="B19:F19"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A18:F18"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
